--- a/Data/Terminator_Strength-250423-1.xlsx
+++ b/Data/Terminator_Strength-250423-1.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uob-my.sharepoint.com/personal/zw24976_bristol_ac_uk/Documents/Documents/BCL/PhagePol_Terminators/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="90" documentId="8_{7634C380-3AC4-4B80-8552-1087F808F648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25E86506-4DB9-4FA3-AF18-7F5F089F9AF7}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="8_{7634C380-3AC4-4B80-8552-1087F808F648}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82F78915-E901-4319-98C6-AE37DFC5AE6A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{475DD41C-9EC2-475B-95D1-136B7B825981}"/>
   </bookViews>
   <sheets>
-    <sheet name="OD600" sheetId="1" r:id="rId1"/>
-    <sheet name="GFP" sheetId="3" r:id="rId2"/>
-    <sheet name="RFP" sheetId="4" r:id="rId3"/>
+    <sheet name="PlateMap" sheetId="5" r:id="rId1"/>
+    <sheet name="OD600" sheetId="1" r:id="rId2"/>
+    <sheet name="GFP" sheetId="3" r:id="rId3"/>
+    <sheet name="RFP" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7355" uniqueCount="5276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7459" uniqueCount="5380">
   <si>
     <t>Time</t>
   </si>
@@ -15874,6 +15875,318 @@
   </si>
   <si>
     <t>2187</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-20bp</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-20_lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-20_tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-20_G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb1-20_G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-20bp</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-20_lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-20_tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-20_G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-T7hyb8-20_G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-20bp</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-20_lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-20_tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-20_G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S2P11-20_G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-20bp</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-20_lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-20_tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-20_G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-L3S1P00-20_G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-20bp</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-20_lacO</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-20_tetO</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-20_G3T</t>
+  </si>
+  <si>
+    <t>0Cuma-50bp-20_G3Tr</t>
+  </si>
+  <si>
+    <t>0Cuma-RPU</t>
+  </si>
+  <si>
+    <t>0Cuma-AF</t>
+  </si>
+  <si>
+    <t>0Cuma-Blank</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-20bp</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-20_lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-20_tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-20_G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb1-20_G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-20bp</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-20_lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-20_tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-20_G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-T7hyb8-20_G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-20bp</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-20_lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-20_tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-20_G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S2P11-20_G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-20bp</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-20_lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-20_tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-20_G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-L3S1P00-20_G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-20bp</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-20_lacO</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-20_tetO</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-20_G3T</t>
+  </si>
+  <si>
+    <t>10Cuma-50bp-20_G3Tr</t>
+  </si>
+  <si>
+    <t>10Cuma-RPU</t>
+  </si>
+  <si>
+    <t>10Cuma-AF</t>
+  </si>
+  <si>
+    <t>10Cuma-Blank</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
   </si>
 </sst>
 </file>
@@ -15960,10 +16273,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -16282,6 +16591,394 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D827E05D-0CBA-4CC4-BBC7-D5F69576E43A}">
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>2</v>
+      </c>
+      <c r="D1">
+        <v>3</v>
+      </c>
+      <c r="E1">
+        <v>4</v>
+      </c>
+      <c r="F1">
+        <v>5</v>
+      </c>
+      <c r="G1">
+        <v>6</v>
+      </c>
+      <c r="H1">
+        <v>7</v>
+      </c>
+      <c r="I1">
+        <v>8</v>
+      </c>
+      <c r="J1">
+        <v>9</v>
+      </c>
+      <c r="K1">
+        <v>10</v>
+      </c>
+      <c r="L1">
+        <v>11</v>
+      </c>
+      <c r="M1">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>5372</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5276</v>
+      </c>
+      <c r="C2" t="s">
+        <v>5277</v>
+      </c>
+      <c r="D2" t="s">
+        <v>5278</v>
+      </c>
+      <c r="E2" t="s">
+        <v>5279</v>
+      </c>
+      <c r="F2" t="s">
+        <v>5280</v>
+      </c>
+      <c r="G2" t="s">
+        <v>5281</v>
+      </c>
+      <c r="H2" t="s">
+        <v>5282</v>
+      </c>
+      <c r="I2" t="s">
+        <v>5283</v>
+      </c>
+      <c r="J2" t="s">
+        <v>5284</v>
+      </c>
+      <c r="K2" t="s">
+        <v>5285</v>
+      </c>
+      <c r="L2" t="s">
+        <v>5286</v>
+      </c>
+      <c r="M2" t="s">
+        <v>5287</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>5373</v>
+      </c>
+      <c r="B3" t="s">
+        <v>5288</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5289</v>
+      </c>
+      <c r="D3" t="s">
+        <v>5290</v>
+      </c>
+      <c r="E3" t="s">
+        <v>5291</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5292</v>
+      </c>
+      <c r="G3" t="s">
+        <v>5293</v>
+      </c>
+      <c r="H3" t="s">
+        <v>5294</v>
+      </c>
+      <c r="I3" t="s">
+        <v>5295</v>
+      </c>
+      <c r="J3" t="s">
+        <v>5296</v>
+      </c>
+      <c r="K3" t="s">
+        <v>5297</v>
+      </c>
+      <c r="L3" t="s">
+        <v>5298</v>
+      </c>
+      <c r="M3" t="s">
+        <v>5299</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>5374</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5300</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5301</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5302</v>
+      </c>
+      <c r="E4" t="s">
+        <v>5303</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5304</v>
+      </c>
+      <c r="G4" t="s">
+        <v>5305</v>
+      </c>
+      <c r="H4" t="s">
+        <v>5306</v>
+      </c>
+      <c r="I4" t="s">
+        <v>5307</v>
+      </c>
+      <c r="J4" t="s">
+        <v>5308</v>
+      </c>
+      <c r="K4" t="s">
+        <v>5309</v>
+      </c>
+      <c r="L4" t="s">
+        <v>5310</v>
+      </c>
+      <c r="M4" t="s">
+        <v>5311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>5375</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5312</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5313</v>
+      </c>
+      <c r="D5" t="s">
+        <v>5314</v>
+      </c>
+      <c r="E5" t="s">
+        <v>5315</v>
+      </c>
+      <c r="F5" t="s">
+        <v>5316</v>
+      </c>
+      <c r="G5" t="s">
+        <v>5317</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5318</v>
+      </c>
+      <c r="I5" t="s">
+        <v>5319</v>
+      </c>
+      <c r="J5" t="s">
+        <v>5320</v>
+      </c>
+      <c r="K5" t="s">
+        <v>5321</v>
+      </c>
+      <c r="L5" t="s">
+        <v>5322</v>
+      </c>
+      <c r="M5" t="s">
+        <v>5323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>5376</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5324</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5325</v>
+      </c>
+      <c r="D6" t="s">
+        <v>5326</v>
+      </c>
+      <c r="E6" t="s">
+        <v>5327</v>
+      </c>
+      <c r="F6" t="s">
+        <v>5328</v>
+      </c>
+      <c r="G6" t="s">
+        <v>5329</v>
+      </c>
+      <c r="H6" t="s">
+        <v>5330</v>
+      </c>
+      <c r="I6" t="s">
+        <v>5331</v>
+      </c>
+      <c r="J6" t="s">
+        <v>5332</v>
+      </c>
+      <c r="K6" t="s">
+        <v>5333</v>
+      </c>
+      <c r="L6" t="s">
+        <v>5334</v>
+      </c>
+      <c r="M6" t="s">
+        <v>5335</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>5377</v>
+      </c>
+      <c r="B7" t="s">
+        <v>5336</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5337</v>
+      </c>
+      <c r="D7" t="s">
+        <v>5338</v>
+      </c>
+      <c r="E7" t="s">
+        <v>5339</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5340</v>
+      </c>
+      <c r="G7" t="s">
+        <v>5341</v>
+      </c>
+      <c r="H7" t="s">
+        <v>5342</v>
+      </c>
+      <c r="I7" t="s">
+        <v>5343</v>
+      </c>
+      <c r="J7" t="s">
+        <v>5344</v>
+      </c>
+      <c r="K7" t="s">
+        <v>5345</v>
+      </c>
+      <c r="L7" t="s">
+        <v>5346</v>
+      </c>
+      <c r="M7" t="s">
+        <v>5347</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>5378</v>
+      </c>
+      <c r="B8" t="s">
+        <v>5348</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5349</v>
+      </c>
+      <c r="D8" t="s">
+        <v>5350</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5351</v>
+      </c>
+      <c r="F8" t="s">
+        <v>5352</v>
+      </c>
+      <c r="G8" t="s">
+        <v>5353</v>
+      </c>
+      <c r="H8" t="s">
+        <v>5354</v>
+      </c>
+      <c r="I8" t="s">
+        <v>5355</v>
+      </c>
+      <c r="J8" t="s">
+        <v>5356</v>
+      </c>
+      <c r="K8" t="s">
+        <v>5357</v>
+      </c>
+      <c r="L8" t="s">
+        <v>5358</v>
+      </c>
+      <c r="M8" t="s">
+        <v>5359</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>5379</v>
+      </c>
+      <c r="B9" t="s">
+        <v>5360</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5361</v>
+      </c>
+      <c r="D9" t="s">
+        <v>5362</v>
+      </c>
+      <c r="E9" t="s">
+        <v>5363</v>
+      </c>
+      <c r="F9" t="s">
+        <v>5364</v>
+      </c>
+      <c r="G9" t="s">
+        <v>5365</v>
+      </c>
+      <c r="H9" t="s">
+        <v>5366</v>
+      </c>
+      <c r="I9" t="s">
+        <v>5367</v>
+      </c>
+      <c r="J9" t="s">
+        <v>5368</v>
+      </c>
+      <c r="K9" t="s">
+        <v>5369</v>
+      </c>
+      <c r="L9" t="s">
+        <v>5370</v>
+      </c>
+      <c r="M9" t="s">
+        <v>5371</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0570F820-A9DB-4373-ADDC-34E068AA7F43}">
   <dimension ref="A1:CT26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -23987,7 +24684,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34C910BC-0834-4341-BF10-2CF501F62A4F}">
   <dimension ref="A1:CT26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -31691,7 +32388,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FEAD6E7-3FFE-4D18-A17B-6DA3CBE7C8D7}">
   <dimension ref="A1:CT26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
